--- a/data/trans_bre/CAGE_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/CAGE_R-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,42</t>
+          <t>-0,39; 1,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; -0,99</t>
+          <t>-3,75; -0,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,76</t>
+          <t>-1,6; 2,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 1,0</t>
+          <t>-3,12; 1,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 133,07</t>
+          <t>-100,0; 153,86</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,33</t>
+          <t>-3,19; 0,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,44</t>
+          <t>-1,33; 1,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 3,92</t>
+          <t>-0,57; 4,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,19; 4635,71</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; -0,3</t>
+          <t>-1,77; -0,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,47; -0,9</t>
+          <t>-3,85; -0,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,39</t>
+          <t>-2,2; 2,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,94; -1,32</t>
+          <t>-6,37; -1,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 426,78</t>
+          <t>-100,0; 303,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,06</t>
+          <t>-1,44; 0,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,88; -1,1</t>
+          <t>-2,93; -1,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,12; -0,39</t>
+          <t>-2,16; -0,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -0,73</t>
+          <t>-4,58; -0,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 54,57</t>
+          <t>-100,0; 53,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -59,33</t>
+          <t>-100,0; -54,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-95,35; -24,14</t>
+          <t>-95,53; -19,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -36,41</t>
+          <t>-100,0; -33,02</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,77</t>
+          <t>-1,76; 0,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; -0,52</t>
+          <t>-3,01; -0,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,68; -0,54</t>
+          <t>-2,49; -0,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,05</t>
+          <t>-3,94; 1,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 412,69</t>
+          <t>-100,0; 295,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -38,38</t>
+          <t>-100,0; -24,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -13,25</t>
+          <t>-100,0; -8,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-83,45; 157,63</t>
+          <t>-82,48; 123,67</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,16</t>
+          <t>-1,9; 0,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,22; -0,98</t>
+          <t>-5,23; -1,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,07; -0,43</t>
+          <t>-3,6; -0,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,41</t>
+          <t>0,0; 9,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -55,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-96,96; -28,62</t>
+          <t>-97,09; -9,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; -0,15</t>
+          <t>-0,94; -0,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; -1,29</t>
+          <t>-2,29; -1,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; -0,43</t>
+          <t>-1,51; -0,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,09</t>
+          <t>-2,12; 0,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-86,48; -19,83</t>
+          <t>-87,77; -19,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-97,61; -81,95</t>
+          <t>-97,39; -82,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-82,47; -35,68</t>
+          <t>-82,29; -41,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-78,49; 4,26</t>
+          <t>-77,04; 3,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/CAGE_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/CAGE_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,04</t>
+          <t>-1,63</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-45,77%</t>
+          <t>-58,13%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,47</t>
+          <t>-0,39; 1,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; -0,84</t>
+          <t>-3,79; -0,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,02</t>
+          <t>-1,71; 1,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,12</t>
+          <t>-4,04; 0,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 153,86</t>
+          <t>-100,0; 69,56</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>155,35%</t>
+          <t>120,37%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,55</t>
+          <t>-1,41; 0,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,34</t>
+          <t>-3,28; 0,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,55</t>
+          <t>-1,38; 1,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,06</t>
+          <t>-0,86; 4,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,19; 4635,71</t>
+          <t>-80,55; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,81</t>
+          <t>-3,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; -0,31</t>
+          <t>-1,94; -0,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,85; -0,94</t>
+          <t>-3,49; -0,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,33</t>
+          <t>-2,09; 2,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -1,13</t>
+          <t>-7,85; -1,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 303,46</t>
+          <t>-100,0; 333,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,22</t>
+          <t>-0,5</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-81,87%</t>
+          <t>-21,55%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,06</t>
+          <t>-1,47; 0,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,93; -1,14</t>
+          <t>-2,8; -1,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,16; -0,37</t>
+          <t>-2,04; -0,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,58; -0,61</t>
+          <t>-2,46; 3,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 53,63</t>
+          <t>-100,0; 62,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -54,51</t>
+          <t>-100,0; -58,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-95,53; -19,8</t>
+          <t>-100,0; -21,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -33,02</t>
+          <t>-85,6; 223,43</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,05</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-33,18%</t>
+          <t>-43,9%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,77</t>
+          <t>-1,82; 0,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; -0,56</t>
+          <t>-3,08; -0,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; -0,49</t>
+          <t>-2,52; -0,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 1,59</t>
+          <t>-4,62; 1,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 295,29</t>
+          <t>-100,0; 390,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -24,75</t>
+          <t>-100,0; -41,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -8,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-82,48; 123,67</t>
+          <t>-84,54; 79,79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,16</t>
+          <t>-1,43; 0,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -1,03</t>
+          <t>-5,18; -0,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,6; -0,36</t>
+          <t>-3,83; -0,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,39</t>
+          <t>0,0; 9,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -55,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-97,09; -9,02</t>
+          <t>-96,43; -23,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,1</t>
+          <t>-0,74</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-48,32%</t>
+          <t>-30,09%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; -0,18</t>
+          <t>-0,9; -0,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; -1,29</t>
+          <t>-2,37; -1,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; -0,51</t>
+          <t>-1,49; -0,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,04</t>
+          <t>-1,82; 0,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-87,77; -19,06</t>
+          <t>-85,88; -12,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-97,39; -82,12</t>
+          <t>-97,45; -81,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-82,29; -41,87</t>
+          <t>-82,55; -41,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-77,04; 3,09</t>
+          <t>-61,99; 33,7</t>
         </is>
       </c>
     </row>
